--- a/education_forms/019_student_covid_19_self_certification_and_verification_form--education_forms.xlsx
+++ b/education_forms/019_student_covid_19_self_certification_and_verification_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>new_or_worsening_confusion_or_changing_mental_status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>New or worsening confusion or changing mental status</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>new_or_worsening_confusion_or_changing_mental_status</t>
+          <t>new_or_worsening_confusion_or_change_in_mental_status</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New or worsening confusion or changing mental status</t>
+          <t>New or worsening confusion or change in mental status</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>new_or_worsening_confusion_or_change_in_mental_status</t>
+          <t>new_or_worsening_confusion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New or worsening confusion or change in mental status</t>
+          <t>New or worsening confusion</t>
         </is>
       </c>
     </row>
@@ -1063,87 +1063,87 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>new_or_worsening_confusion</t>
+          <t>new_or_worsening_change_in_mental_status</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New or worsening confusion</t>
+          <t>New or worsening change in mental status</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_2_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>new_or_worsening_change_in_mental_status</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New or worsening change in mental status</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_2_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>new_or_worsening_confusion_or_change_in_mental_status</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New or worsening confusion or change in mental status</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_2_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>new_or_worsening_confusion</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New or worsening confusion</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_2_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>new_or_worsening_change_in_mental_status</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New or worsening change in mental status</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_3_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_5_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_3_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_5_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_4_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_6_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_4_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_6_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_5_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_8_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_5_choices</t>
+          <t>student_covid_19_self_certification_and_verification_form_page_8_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1237,74 +1237,6 @@
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>student_covid_19_self_certification_and_verification_form_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>False</t>
         </is>
